--- a/venture/07-automation/tracker/publish-queue/debt-payoff-planner-v1/Debt-Payoff-Planner.xlsx
+++ b/venture/07-automation/tracker/publish-queue/debt-payoff-planner-v1/Debt-Payoff-Planner.xlsx
@@ -550,7 +550,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3. The Snowball and Avalanche tabs show payoff months and estimated interest for each strategy.</t>
+          <t>3. The Snowball and Avalanche tabs show the payoff months for each debt under each strategy.</t>
         </is>
       </c>
     </row>
